--- a/server/src/data/西班牙语单词本-形容词.xlsx
+++ b/server/src/data/西班牙语单词本-形容词.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ydy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的项目\业务mvp\vocabulario-espanol\server\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C261B24A-ED10-4BE3-AA77-E8737A079F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB54D0A-94D3-447F-B0A7-546097BF6A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32070" yWindow="2745" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33675" yWindow="1200" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="形容词表" sheetId="3" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="535">
   <si>
     <t>原形</t>
   </si>
@@ -45,24 +45,6 @@
     <t>拓展搭配 &amp; 语法要点</t>
   </si>
   <si>
-    <t>原形</t>
-  </si>
-  <si>
-    <t>中文释义</t>
-  </si>
-  <si>
-    <t>文中变位/形式</t>
-  </si>
-  <si>
-    <t>中文情景句</t>
-  </si>
-  <si>
-    <t>西语原句</t>
-  </si>
-  <si>
-    <t>拓展搭配 &amp; 语法要点</t>
-  </si>
-  <si>
     <t>Rapido/a</t>
   </si>
   <si>
@@ -72,10 +54,10 @@
     <t>rapido（原形）</t>
   </si>
   <si>
-    <t>人生是一场旅程：时而快</t>
-  </si>
-  <si>
-    <t>La vida es un viaje: a veces rapido</t>
+    <t>人生是一场旅程：时而快。</t>
+  </si>
+  <si>
+    <t>La vida es un viaje: a veces rapido.</t>
   </si>
   <si>
     <t>-o/a结尾形容词，阴阳性变化；副词形式rápidamente</t>
@@ -90,10 +72,10 @@
     <t>lento（原形）</t>
   </si>
   <si>
-    <t>时常慢</t>
-  </si>
-  <si>
-    <t>a menudo lento</t>
+    <t>他时常慢。</t>
+  </si>
+  <si>
+    <t>Él a menudo lento.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；副词形式lentamente</t>
@@ -105,13 +87,13 @@
     <t>早的</t>
   </si>
   <si>
-    <t>temprano（原形）</t>
-  </si>
-  <si>
-    <t>无关你出发得早</t>
-  </si>
-  <si>
-    <t>No importa si empiezas temprano</t>
+    <t>temprano（原形） | 阳性: Temprano | 阴性: Temprana</t>
+  </si>
+  <si>
+    <t>无关你出发得早。</t>
+  </si>
+  <si>
+    <t>Él No importa si empiezas temprano.</t>
   </si>
   <si>
     <t>无阴阳性变化；可作形容词/副词</t>
@@ -123,16 +105,13 @@
     <t>迟的</t>
   </si>
   <si>
-    <t>tarde（原形）</t>
-  </si>
-  <si>
-    <t>或到得迟</t>
-  </si>
-  <si>
-    <t>o llegas tarde</t>
-  </si>
-  <si>
-    <t>无阴阳性变化；可作形容词/副词</t>
+    <t>tarde（原形） | 阴阳性同形: Tarde</t>
+  </si>
+  <si>
+    <t>他或到得迟。</t>
+  </si>
+  <si>
+    <t>Él o llegas tarde.</t>
   </si>
   <si>
     <t>Joven</t>
@@ -144,10 +123,10 @@
     <t>joven（原形）</t>
   </si>
   <si>
-    <t>一份年轻的爱可以栖居于被生活磨旧的心中</t>
-  </si>
-  <si>
-    <t>un amor joven puede habitar en un corazón usado por la vida</t>
+    <t>一份年轻的爱可以栖居于被生活磨旧的心中。</t>
+  </si>
+  <si>
+    <t>Él un amor joven puede habitar en un corazón usado por la vida.</t>
   </si>
   <si>
     <t>无阴阳性变化；复数jóvenes</t>
@@ -162,10 +141,10 @@
     <t>anciana（原形）</t>
   </si>
   <si>
-    <t>一道年深日久的伤痕</t>
-  </si>
-  <si>
-    <t>una herida anciana</t>
+    <t>他一道年深日久的伤痕。</t>
+  </si>
+  <si>
+    <t>Él una herida anciana.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词joven</t>
@@ -180,10 +159,10 @@
     <t>nueva（原形）</t>
   </si>
   <si>
-    <t>一个崭新的诺言可以治愈一道年深日久的伤痕</t>
-  </si>
-  <si>
-    <t>Una promesa nueva puede sanar una herida anciana</t>
+    <t>他一个崭新的诺言可以治愈一道年深日久的伤痕。</t>
+  </si>
+  <si>
+    <t>Él Una promesa nueva puede sanar una herida anciana.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词viejo</t>
@@ -198,10 +177,10 @@
     <t>usado（原形）</t>
   </si>
   <si>
-    <t>被生活磨旧的心中</t>
-  </si>
-  <si>
-    <t>un corazón usado por la vida</t>
+    <t>被生活磨旧的心中。</t>
+  </si>
+  <si>
+    <t>Él un corazón usado por la vida.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词nuevo</t>
@@ -216,10 +195,10 @@
     <t>calurosa（原形）</t>
   </si>
   <si>
-    <t>在这座潮湿的城市，连夜晚都闷热</t>
-  </si>
-  <si>
-    <t>En esta ciudad húmeda, incluso la noche es calurosa</t>
+    <t>他在这座潮湿的城市，连夜晚都闷热。</t>
+  </si>
+  <si>
+    <t>Él En esta ciudad húmeda, incluso la noche es calurosa.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；仅用于天气</t>
@@ -234,10 +213,10 @@
     <t>fresco（原形）</t>
   </si>
   <si>
-    <t>即便是正午也可能凉爽</t>
-  </si>
-  <si>
-    <t>alli, hasta el mediodia podia ser fresco</t>
+    <t>他即便是正午也可能凉爽。</t>
+  </si>
+  <si>
+    <t>Él alli, hasta el mediodia podia ser fresco.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词caluroso</t>
@@ -252,10 +231,10 @@
     <t>seco（原形）</t>
   </si>
   <si>
-    <t>我梦寐高原干燥的风</t>
-  </si>
-  <si>
-    <t>sueno con el viento seco de la meseta</t>
+    <t>我梦寐高原干燥的风。</t>
+  </si>
+  <si>
+    <t>Él sueno con el viento seco de la meseta.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词húmedo</t>
@@ -270,10 +249,10 @@
     <t>húmeda（原形）</t>
   </si>
   <si>
-    <t>在这座潮湿的城市</t>
-  </si>
-  <si>
-    <t>En esta ciudad húmeda</t>
+    <t>他在这座潮湿的城市。</t>
+  </si>
+  <si>
+    <t>Él En esta ciudad húmeda.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词seco</t>
@@ -288,10 +267,10 @@
     <t>duro（原形）</t>
   </si>
   <si>
-    <t>冬日的坚硬大地被柔软的雪毯覆盖</t>
-  </si>
-  <si>
-    <t>El suelo duro de invierno se cubre con un manto blando</t>
+    <t>他冬日的坚硬大地被柔软的雪毯覆盖。</t>
+  </si>
+  <si>
+    <t>El suelo duro de invierno se cubre con un manto blando.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词blando</t>
@@ -306,10 +285,10 @@
     <t>blando（原形）</t>
   </si>
   <si>
-    <t>被柔软的雪毯覆盖</t>
-  </si>
-  <si>
-    <t>un manto blando</t>
+    <t>他被柔软的雪毯覆盖。</t>
+  </si>
+  <si>
+    <t>Él un manto blando.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词duro</t>
@@ -324,10 +303,10 @@
     <t>pesada（原形）</t>
   </si>
   <si>
-    <t>堆积起来却变得沉重</t>
-  </si>
-  <si>
-    <t>acumulada se hace pesada</t>
+    <t>他堆积起来却变得沉重。</t>
+  </si>
+  <si>
+    <t>Él acumulada se hace pesada.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词liviano</t>
@@ -342,10 +321,10 @@
     <t>liviana（原形）</t>
   </si>
   <si>
-    <t>初雪飘落时很轻盈</t>
-  </si>
-  <si>
-    <t>La primera nieve cae liviana</t>
+    <t>他初雪飘落时很轻盈。</t>
+  </si>
+  <si>
+    <t>La primera nieve cae liviana.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词pesado</t>
@@ -360,10 +339,10 @@
     <t>abierta（原形）</t>
   </si>
   <si>
-    <t>清晨它会再度敞开</t>
-  </si>
-  <si>
-    <t>Por la manana volvería a estar abierta</t>
+    <t>清晨它会再度敞开。</t>
+  </si>
+  <si>
+    <t>Él Por la manana volvería a estar abierta.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词cerrado</t>
@@ -378,10 +357,10 @@
     <t>cerrada（原形）</t>
   </si>
   <si>
-    <t>书店已经打烊</t>
-  </si>
-  <si>
-    <t>La libreriía ya estaba cerrada</t>
+    <t>他书店已经打烊。</t>
+  </si>
+  <si>
+    <t>La libreriía ya estaba cerrada.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词abierto</t>
@@ -396,10 +375,10 @@
     <t>llena（原形）</t>
   </si>
   <si>
-    <t>满载着等待读者的故事</t>
-  </si>
-  <si>
-    <t>llena de historias esperando lectores</t>
+    <t>他满载着等待读者的故事。</t>
+  </si>
+  <si>
+    <t>Él llena de historias esperando lectores.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词vacío</t>
@@ -414,10 +393,10 @@
     <t>vacio（原形）</t>
   </si>
   <si>
-    <t>橱窗空空如也</t>
-  </si>
-  <si>
-    <t>su escaparate vacio</t>
+    <t>他橱窗空空如也。</t>
+  </si>
+  <si>
+    <t>Él su escaparate vacio.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词lleno</t>
@@ -432,10 +411,10 @@
     <t>limpia（原形）</t>
   </si>
   <si>
-    <t>但他们的笑声让灵魂纯净</t>
-  </si>
-  <si>
-    <t>pero sus risas dejan el alma limpia</t>
+    <t>但他们的笑声让灵魂纯净。</t>
+  </si>
+  <si>
+    <t>Él pero sus risas dejan el alma limpia.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词manchado</t>
@@ -450,10 +429,10 @@
     <t>manchadas（原形）</t>
   </si>
   <si>
-    <t>孩子们回家时衣服沾满泥点</t>
-  </si>
-  <si>
-    <t>Los ninos vuelven a casa con ropas manchadas de barro</t>
+    <t>他孩子们回家时衣服沾满泥点。</t>
+  </si>
+  <si>
+    <t>Los ninos vuelven a casa con ropas manchadas de barro.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词limpio</t>
@@ -468,10 +447,10 @@
     <t>ordenado（原形）</t>
   </si>
   <si>
-    <t>让一天完美有序</t>
-  </si>
-  <si>
-    <t>y el dia perfectamente ordenado</t>
+    <t>他让一天完美有序。</t>
+  </si>
+  <si>
+    <t>Él y el dia perfectamente ordenado.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词desordenado</t>
@@ -486,10 +465,10 @@
     <t>desordenadas（原形）</t>
   </si>
   <si>
-    <t>房间变得凌乱</t>
-  </si>
-  <si>
-    <t>y habitaciones desordenadas</t>
+    <t>他房间变得凌乱。</t>
+  </si>
+  <si>
+    <t>Él y habitaciones desordenadas.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词ordenado</t>
@@ -504,10 +483,10 @@
     <t>delgada（原形）</t>
   </si>
   <si>
-    <t>无论是纤细的法棍还是圆胖的乡村面包</t>
-  </si>
-  <si>
-    <t>No importa si es una baguette delgada o un pan rellenito de pueblo</t>
+    <t>他无论是纤细的法棍还是圆胖的乡村面包。</t>
+  </si>
+  <si>
+    <t>Él No importa si es una baguette delgada o un pan rellenito de pueblo.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词rellenito</t>
@@ -522,12 +501,6 @@
     <t>rellenito（原形）</t>
   </si>
   <si>
-    <t>无论是纤细的法棍还是圆胖的乡村面包</t>
-  </si>
-  <si>
-    <t>No importa si es una baguette delgada o un pan rellenito de pueblo</t>
-  </si>
-  <si>
     <t>-o/a结尾形容词；反义词delgado</t>
   </si>
   <si>
@@ -537,13 +510,13 @@
     <t>热的</t>
   </si>
   <si>
-    <t>caliente（原形）</t>
-  </si>
-  <si>
-    <t>刚出炉的面包外皮滚烫酥脆</t>
-  </si>
-  <si>
-    <t>El pan recién horneado está caliente y crujiente por fuera</t>
+    <t>caliente（原形） | 阴阳性同形: Caliente</t>
+  </si>
+  <si>
+    <t>他刚出炉的面包外皮滚烫酥脆。</t>
+  </si>
+  <si>
+    <t>El pan recién horneado está caliente y crujiente por fuera.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词frío</t>
@@ -558,10 +531,10 @@
     <t>frio（原形）</t>
   </si>
   <si>
-    <t>最适合寒冷的天气</t>
-  </si>
-  <si>
-    <t>perfecto para un dia frio</t>
+    <t>他最适合寒冷的天气。</t>
+  </si>
+  <si>
+    <t>Él perfecto para un dia frio.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词caliente</t>
@@ -576,10 +549,10 @@
     <t>cerca（原形）</t>
   </si>
   <si>
-    <t>今天看似近在眼前的</t>
-  </si>
-  <si>
-    <t>Lo que hoy parece cerca</t>
+    <t>他今天看似近在眼前的。</t>
+  </si>
+  <si>
+    <t>Él Lo que hoy parece cerca.</t>
   </si>
   <si>
     <t>无阴阳性变化；可作形容词/副词；反义词lejano</t>
@@ -594,10 +567,10 @@
     <t>lejano（原形）</t>
   </si>
   <si>
-    <t>星辰很遥远</t>
-  </si>
-  <si>
-    <t>Las estrellas estan lejanas</t>
+    <t>他星辰很遥远。</t>
+  </si>
+  <si>
+    <t>Las estrellas estan lejanas.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词cerca</t>
@@ -612,10 +585,10 @@
     <t>altas（原形）</t>
   </si>
   <si>
-    <t>最高大的事物都始于最微小的根基</t>
-  </si>
-  <si>
-    <t>Las cosas más altas empiezan desde lo más bajito</t>
+    <t>他最高大的事物都始于最微小的根基。</t>
+  </si>
+  <si>
+    <t>Las cosas más altas empiezan desde lo más bajito.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词bajo</t>
@@ -630,12 +603,6 @@
     <t>bajito（原形）</t>
   </si>
   <si>
-    <t>最高大的事物都始于最微小的根基</t>
-  </si>
-  <si>
-    <t>Las cosas más altas empiezan desde lo más bajito</t>
-  </si>
-  <si>
     <t>-o/a结尾形容词；反义词alto</t>
   </si>
   <si>
@@ -648,10 +615,10 @@
     <t>guapo（原形）</t>
   </si>
   <si>
-    <t>一段充满理解的、丰盈的爱情，比千言万语都更美好</t>
-  </si>
-  <si>
-    <t>Un amor rico en comprensión es más guapo que mil palabras</t>
+    <t>他一段充满理解的、丰盈的爱情，比千言万语都更美好。</t>
+  </si>
+  <si>
+    <t>Él Un amor rico en comprensión es más guapo que mil palabras.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词horrible</t>
@@ -663,13 +630,13 @@
     <t>可怕的</t>
   </si>
   <si>
-    <t>horrible（原形）</t>
-  </si>
-  <si>
-    <t>则会变成一场可怕的噩梦</t>
-  </si>
-  <si>
-    <t>se convierte en una pesadilla horrible</t>
+    <t>horrible（原形） | 阴阳性同形: Horrible</t>
+  </si>
+  <si>
+    <t>他则会变成一场可怕的噩梦。</t>
+  </si>
+  <si>
+    <t>Él se convierte en una pesadilla horrible.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词guapo</t>
@@ -684,10 +651,10 @@
     <t>rico（原形）</t>
   </si>
   <si>
-    <t>一段充满理解的、丰盈的爱情</t>
-  </si>
-  <si>
-    <t>Un amor rico en comprensión</t>
+    <t>他一段充满理解的、丰盈的爱情。</t>
+  </si>
+  <si>
+    <t>Él Un amor rico en comprensión.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词pobre</t>
@@ -699,13 +666,13 @@
     <t>贫穷的</t>
   </si>
   <si>
-    <t>pobre（原形）</t>
-  </si>
-  <si>
-    <t>一段缺乏尊重的、贫瘠的爱情</t>
-  </si>
-  <si>
-    <t>un amor pobre en respeto</t>
+    <t>pobre（原形） | 阴阳性同形: Pobre</t>
+  </si>
+  <si>
+    <t>他一段缺乏尊重的、贫瘠的爱情。</t>
+  </si>
+  <si>
+    <t>Él un amor pobre en respeto.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词rico</t>
@@ -720,10 +687,10 @@
     <t>satisfechas（原形）</t>
   </si>
   <si>
-    <t>一段健康的关系让双方都感到满足并共同成长</t>
-  </si>
-  <si>
-    <t>Una relación saludable deja a ambas partes satisfechas y en crecimiento</t>
+    <t>他一段健康的关系让双方都感到满足并共同成长。</t>
+  </si>
+  <si>
+    <t>Él Una relación saludable deja a ambas partes satisfechas y en crecimiento.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词disgustado</t>
@@ -738,10 +705,10 @@
     <t>disgustadas（原形）</t>
   </si>
   <si>
-    <t>一段病态的关系则让人不快且情感耗竭</t>
-  </si>
-  <si>
-    <t>una relación enfermiza deja a las personas disgustadas y emocionalmente agotadas</t>
+    <t>他一段病态的关系则让人不快且情感耗竭。</t>
+  </si>
+  <si>
+    <t>Él una relación enfermiza deja a las personas disgustadas y emocionalmente agotadas.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词satisfecho</t>
@@ -753,13 +720,7 @@
     <t>健康的</t>
   </si>
   <si>
-    <t>saludable（原形）</t>
-  </si>
-  <si>
-    <t>一段健康的关系让双方都感到满足并共同成长</t>
-  </si>
-  <si>
-    <t>Una relación saludable deja a ambas partes satisfechas y en crecimiento</t>
+    <t>saludable（原形） | 阴阳性同形: Saludable</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词enfermizo</t>
@@ -774,12 +735,6 @@
     <t>enfermiza（原形）</t>
   </si>
   <si>
-    <t>一段病态的关系则让人不快且情感耗竭</t>
-  </si>
-  <si>
-    <t>una relación enfermiza deja a las personas disgustadas y emocionalmente agotadas</t>
-  </si>
-  <si>
     <t>-o/a结尾形容词；反义词saludable</t>
   </si>
   <si>
@@ -789,13 +744,13 @@
     <t>有趣的</t>
   </si>
   <si>
-    <t>interesante（原形）</t>
-  </si>
-  <si>
-    <t>一部有趣的电影并不需要总是欢快的</t>
-  </si>
-  <si>
-    <t>Una pelicula interesante no necesita ser siempre alegre</t>
+    <t>interesante（原形） | 阴阳性同形: interesante</t>
+  </si>
+  <si>
+    <t>他一部有趣的电影并不需要总是欢快的。</t>
+  </si>
+  <si>
+    <t>Él Una pelicula interesante no necesita ser siempre alegre.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词soso</t>
@@ -810,10 +765,10 @@
     <t>soso（原形）</t>
   </si>
   <si>
-    <t>一个快乐却平淡的结局</t>
-  </si>
-  <si>
-    <t>uno feliz pero SOSO</t>
+    <t>他一个快乐却平淡的结局。</t>
+  </si>
+  <si>
+    <t>Él uno feliz pero SOSO.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词interesante</t>
@@ -825,13 +780,7 @@
     <t>欢快的</t>
   </si>
   <si>
-    <t>alegre（原形）</t>
-  </si>
-  <si>
-    <t>一部有趣的电影并不需要总是欢快的</t>
-  </si>
-  <si>
-    <t>Una pelicula interesante no necesita ser siempre alegre</t>
+    <t>alegre（原形） | 阴阳性同形: Alegre</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词melancólico</t>
@@ -846,10 +795,10 @@
     <t>melancolico（原形）</t>
   </si>
   <si>
-    <t>一个忧郁的结局可能比一个快乐却平淡的结局更令人难忘</t>
-  </si>
-  <si>
-    <t>un final melancolico puede ser más memorable que uno feliz pero SOSO</t>
+    <t>他一个忧郁的结局可能比一个快乐却平淡的结局更令人难忘。</t>
+  </si>
+  <si>
+    <t>Él un final melancolico puede ser más memorable que uno feliz pero SOSO.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词alegre</t>
@@ -864,10 +813,10 @@
     <t>tranquilo（原形）</t>
   </si>
   <si>
-    <t>黎明时公园很宁静</t>
-  </si>
-  <si>
-    <t>El parque está tranquilo al amanecer</t>
+    <t>他黎明时公园很宁静。</t>
+  </si>
+  <si>
+    <t>El parque está tranquilo al amanecer.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词alborotado</t>
@@ -882,10 +831,10 @@
     <t>alborotado（原形）</t>
   </si>
   <si>
-    <t>夜晚，附近的酒吧变得喧闹</t>
-  </si>
-  <si>
-    <t>por la noche, el bar cercano se vuelve alborotado</t>
+    <t>他夜晚，附近的酒吧变得喧闹。</t>
+  </si>
+  <si>
+    <t>Él por la noche, el bar cercano se vuelve alborotado.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词tranquilo</t>
@@ -900,10 +849,10 @@
     <t>seguro（原形）</t>
   </si>
   <si>
-    <t>白天走路很安全</t>
-  </si>
-  <si>
-    <t>Caminar de dia es seguro</t>
+    <t>他白天走路很安全。</t>
+  </si>
+  <si>
+    <t>Él Caminar de dia es seguro.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词arriesgado</t>
@@ -918,10 +867,10 @@
     <t>arriesgada（原形）</t>
   </si>
   <si>
-    <t>但那条小巷在夜里看来却危机四伏</t>
-  </si>
-  <si>
-    <t>pero esa callejuela de noche parece arriesgada</t>
+    <t>他但那条小巷在夜里看来却危机四伏。</t>
+  </si>
+  <si>
+    <t>Él pero esa callejuela de noche parece arriesgada.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词seguro</t>
@@ -936,10 +885,10 @@
     <t>largo（原形）</t>
   </si>
   <si>
-    <t>长长而坚韧</t>
-  </si>
-  <si>
-    <t>largo y resistente</t>
+    <t>他长长而坚韧。</t>
+  </si>
+  <si>
+    <t>Él largo y resistente.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词corto</t>
@@ -954,10 +903,10 @@
     <t>cortos（原形）</t>
   </si>
   <si>
-    <t>串起短暂的瞬间</t>
-  </si>
-  <si>
-    <t>que une momentos cortos</t>
+    <t>他串起短暂的瞬间。</t>
+  </si>
+  <si>
+    <t>Él que une momentos cortos.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词largo</t>
@@ -972,10 +921,10 @@
     <t>grueso（原形）</t>
   </si>
   <si>
-    <t>有时又因时光的重量而变得粗重</t>
-  </si>
-  <si>
-    <t>otras se hace grueso con el peso del tiempo</t>
+    <t>他有时又因时光的重量而变得粗重。</t>
+  </si>
+  <si>
+    <t>Él otras se hace grueso con el peso del tiempo.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词fino</t>
@@ -990,10 +939,10 @@
     <t>fino（原形）</t>
   </si>
   <si>
-    <t>记忆是一根细细的线</t>
-  </si>
-  <si>
-    <t>La memoria es un hilo fino</t>
+    <t>他记忆是一根细细的线。</t>
+  </si>
+  <si>
+    <t>La memoria es un hilo fino.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词grueso</t>
@@ -1005,13 +954,13 @@
     <t>强壮的/强烈的</t>
   </si>
   <si>
-    <t>fuerte（原形）</t>
-  </si>
-  <si>
-    <t>橡树强健抗风</t>
-  </si>
-  <si>
-    <t>EI roble es fuerte contra el viento</t>
+    <t>fuerte（原形） | 阴阳性同形: Fuerte</t>
+  </si>
+  <si>
+    <t>他橡树强健抗风。</t>
+  </si>
+  <si>
+    <t>El roble es fuerte contra el viento.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词débil</t>
@@ -1023,13 +972,13 @@
     <t>虚弱的/微弱的</t>
   </si>
   <si>
-    <t>débil（原形）</t>
-  </si>
-  <si>
-    <t>芦苇柔弱易弯</t>
-  </si>
-  <si>
-    <t>el junco es débil y se dobla</t>
+    <t>débil（原形） | 阴阳性同形: Débil</t>
+  </si>
+  <si>
+    <t>他芦苇柔弱易弯。</t>
+  </si>
+  <si>
+    <t>El junco es débil y se dobla.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词fuerte</t>
@@ -1044,10 +993,10 @@
     <t>ancha（原形）</t>
   </si>
   <si>
-    <t>宽阔的树冠投下荫凉</t>
-  </si>
-  <si>
-    <t>La copa ancha da sombra</t>
+    <t>他宽阔的树冠投下荫凉。</t>
+  </si>
+  <si>
+    <t>La copa ancha da sombra.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词angosto</t>
@@ -1062,10 +1011,10 @@
     <t>angosto（原形）</t>
   </si>
   <si>
-    <t>纤细的树干长得更高</t>
-  </si>
-  <si>
-    <t>el tronco angosto llega alto</t>
+    <t>他纤细的树干长得更高。</t>
+  </si>
+  <si>
+    <t>El tronco angosto llega alto.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词ancho</t>
@@ -1080,10 +1029,10 @@
     <t>trabajador（原形）</t>
   </si>
   <si>
-    <t>那位用新鲜食材创新的勤勉主厨很受食客喜爱</t>
-  </si>
-  <si>
-    <t>El chef trabajador que innovaba con ingredientes frescos era popular entre los comensales</t>
+    <t>他那位用新鲜食材创新的勤勉主厨很受食客喜爱。</t>
+  </si>
+  <si>
+    <t>El chef trabajador que innovaba con ingredientes frescos era popular entre los comensales.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词flojo</t>
@@ -1098,10 +1047,10 @@
     <t>flojo（原形）</t>
   </si>
   <si>
-    <t>那位使用冷冻产品的懈怠主厨则很快变得声名狼藉</t>
-  </si>
-  <si>
-    <t>El chef flojo que usaba productos congelados se volvio impopular rapidamente</t>
+    <t>他那位使用冷冻产品的懈怠主厨则很快变得声名狼藉。</t>
+  </si>
+  <si>
+    <t>El chef flojo que usaba productos congelados se volvio impopular rapidamente.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词trabajador</t>
@@ -1116,10 +1065,7 @@
     <t>popular（原形）</t>
   </si>
   <si>
-    <t>那位用新鲜食材创新的勤勉主厨很受食客喜爱</t>
-  </si>
-  <si>
-    <t>era popular entre los comensales</t>
+    <t>Él era popular entre los comensales.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词impopular</t>
@@ -1134,10 +1080,7 @@
     <t>impopular（原形）</t>
   </si>
   <si>
-    <t>那位使用冷冻产品的懈怠主厨则很快变得声名狼藉</t>
-  </si>
-  <si>
-    <t>se volvio impopular rapidamente</t>
+    <t>Él se volvio impopular rapidamente.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词popular</t>
@@ -1152,10 +1095,10 @@
     <t>optimista（原形）</t>
   </si>
   <si>
-    <t>她乐观又好动，把周末排满了计划</t>
-  </si>
-  <si>
-    <t>Ella, optimista y activa, llenó el fin de semana con planes</t>
+    <t>她乐观又好动，把周末排满了计划。</t>
+  </si>
+  <si>
+    <t>Ella, optimista y activa, llenó el fin de semana con planes.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词pesimista</t>
@@ -1170,10 +1113,10 @@
     <t>pesimista（原形）</t>
   </si>
   <si>
-    <t>他悲观又懒，预言一切都会搞砸</t>
-  </si>
-  <si>
-    <t>EI, pesimista y perezoso, predijo que todos saldrian mal</t>
+    <t>他悲观又懒，预言一切都会搞砸。</t>
+  </si>
+  <si>
+    <t>El, pesimista y perezoso, predijo que todos saldrian mal.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词optimista</t>
@@ -1188,12 +1131,6 @@
     <t>activa（原形）</t>
   </si>
   <si>
-    <t>她乐观又好动，把周末排满了计划</t>
-  </si>
-  <si>
-    <t>Ella, optimista y activa, llenó el fin de semana con planes</t>
-  </si>
-  <si>
     <t>-o/a结尾形容词；反义词perezoso</t>
   </si>
   <si>
@@ -1206,12 +1143,6 @@
     <t>perezoso（原形）</t>
   </si>
   <si>
-    <t>他悲观又懒，预言一切都会搞砸</t>
-  </si>
-  <si>
-    <t>EI, pesimista y perezoso, predijo que todos saldrian mal</t>
-  </si>
-  <si>
     <t>-o/a结尾形容词；反义词activo</t>
   </si>
   <si>
@@ -1221,13 +1152,13 @@
     <t>负责的</t>
   </si>
   <si>
-    <t>responsable（原形）</t>
-  </si>
-  <si>
-    <t>一个负责的人会履行承诺，并细致地关注细节</t>
-  </si>
-  <si>
-    <t>Una persona responsable cumple sus promesas con una atención cuidadosa a los detalles</t>
+    <t>responsable（原形） | 阴阳性同形: Responsable</t>
+  </si>
+  <si>
+    <t>他一个负责的人会履行承诺，并细致地关注细节。</t>
+  </si>
+  <si>
+    <t>Él Una persona responsable cumple sus promesas con una atención cuidadosa a los detalles.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词irresponsable</t>
@@ -1239,13 +1170,13 @@
     <t>不负责任的</t>
   </si>
   <si>
-    <t>irresponsable（原形）</t>
-  </si>
-  <si>
-    <t>一个不负责任的人则会做出轻率的承诺</t>
-  </si>
-  <si>
-    <t>una persona irresponsable hace promesas descuidadas</t>
+    <t>irresponsable（原形） | 阴阳性同形: Irresponsable</t>
+  </si>
+  <si>
+    <t>他一个不负责任的人则会做出轻率的承诺。</t>
+  </si>
+  <si>
+    <t>Él una persona irresponsable hace promesas descuidadas.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词responsable</t>
@@ -1260,10 +1191,10 @@
     <t>cuidadosa（原形）</t>
   </si>
   <si>
-    <t>并细致地关注细节</t>
-  </si>
-  <si>
-    <t>con una atención cuidadosa a los detalles</t>
+    <t>他并细致地关注细节。</t>
+  </si>
+  <si>
+    <t>Él con una atención cuidadosa a los detalles.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词descuidado</t>
@@ -1278,12 +1209,6 @@
     <t>descuidadas（原形）</t>
   </si>
   <si>
-    <t>一个不负责任的人则会做出轻率的承诺</t>
-  </si>
-  <si>
-    <t>una persona irresponsable hace promesas descuidadas</t>
-  </si>
-  <si>
     <t>-o/a结尾形容词；反义词cuidadoso</t>
   </si>
   <si>
@@ -1293,13 +1218,13 @@
     <t>耐心的</t>
   </si>
   <si>
-    <t>paciente（原形）</t>
-  </si>
-  <si>
-    <t>有耐心的艺术家在一件作品上耕耘数年</t>
-  </si>
-  <si>
-    <t>Un artista paciente trabaja anos en una obra</t>
+    <t>paciente（原形） | 阴阳性同形: Paciente</t>
+  </si>
+  <si>
+    <t>他有耐心的艺术家在一件作品上耕耘数年。</t>
+  </si>
+  <si>
+    <t>Él Un artista paciente trabaja anos en una obra.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词impaciente</t>
@@ -1311,13 +1236,13 @@
     <t>不耐烦的</t>
   </si>
   <si>
-    <t>impaciente（原形）</t>
-  </si>
-  <si>
-    <t>没耐心的艺术家则追求快速成功</t>
-  </si>
-  <si>
-    <t>uno impaciente busca el éxito rapido</t>
+    <t>impaciente（原形） | 阴阳性同形: Impaciente</t>
+  </si>
+  <si>
+    <t>他没耐心的艺术家则追求快速成功。</t>
+  </si>
+  <si>
+    <t>Él uno impaciente busca el éxito rapido.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词paciente</t>
@@ -1332,10 +1257,10 @@
     <t>honesto（原形）</t>
   </si>
   <si>
-    <t>最真诚的艺术揭示灵魂</t>
-  </si>
-  <si>
-    <t>El arte más honesto revela el alma</t>
+    <t>他最真诚的艺术揭示灵魂。</t>
+  </si>
+  <si>
+    <t>El arte más honesto revela el alma.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词mentiroso</t>
@@ -1350,10 +1275,10 @@
     <t>mentiroso（原形）</t>
   </si>
   <si>
-    <t>虚假的艺术只是重复潮流</t>
-  </si>
-  <si>
-    <t>el mentiroso solo repite modas</t>
+    <t>他虚假的艺术只是重复潮流。</t>
+  </si>
+  <si>
+    <t>El mentiroso solo repite modas.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词honesto</t>
@@ -1368,10 +1293,10 @@
     <t>generoso（原形）</t>
   </si>
   <si>
-    <t>勇敢的士兵把最后一块饼干分给胆怯的新兵</t>
-  </si>
-  <si>
-    <t>El soldado valiente compartió su última galleta con el recluta cobarde</t>
+    <t>他勇敢的士兵把最后一块饼干分给胆怯的新兵。</t>
+  </si>
+  <si>
+    <t>El soldado valiente compartió su última galleta con el recluta cobarde.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词egoísta</t>
@@ -1386,10 +1311,10 @@
     <t>egoista（原形）</t>
   </si>
   <si>
-    <t>自私的军官把巧克力留给自己</t>
-  </si>
-  <si>
-    <t>El oficial egoista guardaba chocolate para si</t>
+    <t>他自私的军官把巧克力留给自己。</t>
+  </si>
+  <si>
+    <t>El oficial egoista guardaba chocolate para si.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词generoso</t>
@@ -1401,13 +1326,7 @@
     <t>勇敢的</t>
   </si>
   <si>
-    <t>valiente（原形）</t>
-  </si>
-  <si>
-    <t>勇敢的士兵把最后一块饼干分给胆怯的新兵</t>
-  </si>
-  <si>
-    <t>El soldado valiente compartió su última galleta con el recluta cobarde</t>
+    <t>valiente（原形） | 阴阳性同形: Valiente</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词cobarde</t>
@@ -1419,13 +1338,13 @@
     <t>胆小的</t>
   </si>
   <si>
-    <t>cobarde（原形）</t>
-  </si>
-  <si>
-    <t>胆怯的新兵</t>
-  </si>
-  <si>
-    <t>el recluta cobarde</t>
+    <t>cobarde（原形） | 阴阳性同形: Cobarde</t>
+  </si>
+  <si>
+    <t>他胆怯的新兵。</t>
+  </si>
+  <si>
+    <t>El recluta cobarde.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词valiente</t>
@@ -1440,10 +1359,10 @@
     <t>listo（原形）</t>
   </si>
   <si>
-    <t>小精灵非常聪明</t>
-  </si>
-  <si>
-    <t>el duende era muy listo</t>
+    <t>他小精灵非常聪明。</t>
+  </si>
+  <si>
+    <t>El duende era muy listo.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词torpe</t>
@@ -1455,13 +1374,13 @@
     <t>笨拙的</t>
   </si>
   <si>
-    <t>torpe（原形）</t>
-  </si>
-  <si>
-    <t>仙女很友善，但施魔法时有点笨拙</t>
-  </si>
-  <si>
-    <t>el hada era amable pero un poco torpe con su magia</t>
+    <t>torpe（原形） | 阴阳性同形: Torpe</t>
+  </si>
+  <si>
+    <t>他仙女很友善，但施魔法时有点笨拙。</t>
+  </si>
+  <si>
+    <t>El hada era amable pero un poco torpe con su magia.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词listo</t>
@@ -1473,13 +1392,13 @@
     <t>友善的</t>
   </si>
   <si>
-    <t>amable（原形）</t>
-  </si>
-  <si>
-    <t>仙女很友善</t>
-  </si>
-  <si>
-    <t>el hada era amable</t>
+    <t>amable（原形） | 阴阳性同形: Amable</t>
+  </si>
+  <si>
+    <t>他仙女很友善。</t>
+  </si>
+  <si>
+    <t>El hada era amable.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词antipático</t>
@@ -1494,31 +1413,25 @@
     <t>antipatico（原形）</t>
   </si>
   <si>
-    <t>却完全不友善</t>
-  </si>
-  <si>
-    <t>pero completamente antipatico</t>
+    <t>他却完全不友善。</t>
+  </si>
+  <si>
+    <t>Él pero completamente antipatico.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词amable</t>
   </si>
   <si>
-    <t>Nuevo (a)</t>
-  </si>
-  <si>
     <t>新</t>
   </si>
   <si>
     <t>nuevo（原形）</t>
   </si>
   <si>
-    <t>新的晨光从旧屋顶上洒下</t>
-  </si>
-  <si>
-    <t>Un nuevo amanecer se asoma sobre los tejados viejos</t>
-  </si>
-  <si>
-    <t>-o/a结尾形容词；反义词viejo</t>
+    <t>他新的晨光从旧屋顶上洒下。</t>
+  </si>
+  <si>
+    <t>Él Un nuevo amanecer se asoma sobre los tejados viejos.</t>
   </si>
   <si>
     <t>Viejo(a)</t>
@@ -1530,15 +1443,6 @@
     <t>viejos（原形）</t>
   </si>
   <si>
-    <t>新的晨光从旧屋顶上洒下</t>
-  </si>
-  <si>
-    <t>Un nuevo amanecer se asoma sobre los tejados viejos</t>
-  </si>
-  <si>
-    <t>-o/a结尾形容词；反义词nuevo</t>
-  </si>
-  <si>
     <t>Ruidoso (a)</t>
   </si>
   <si>
@@ -1548,46 +1452,31 @@
     <t>ruidosa（原形）</t>
   </si>
   <si>
-    <t>广场虽显得喧闹</t>
-  </si>
-  <si>
-    <t>mientras la plaza parece ruidosa</t>
-  </si>
-  <si>
-    <t>-o/a结尾形容词；反义词tranquilo</t>
-  </si>
-  <si>
-    <t>Tranquilo (a)</t>
+    <t>他广场虽显得喧闹。</t>
+  </si>
+  <si>
+    <t>Él mientras la plaza parece ruidosa.</t>
   </si>
   <si>
     <t>静</t>
   </si>
   <si>
-    <t>tranquilo（原形）</t>
-  </si>
-  <si>
-    <t>心中却自留一方宁静</t>
-  </si>
-  <si>
-    <t>en el corazón se guarda un rincón tranquilo</t>
+    <t>他心中却自留一方宁静。</t>
+  </si>
+  <si>
+    <t>Él en el corazón se guarda un rincón tranquilo.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词ruidoso</t>
   </si>
   <si>
-    <t>Seco(a)</t>
-  </si>
-  <si>
     <t>干</t>
   </si>
   <si>
-    <t>seco（原形）</t>
-  </si>
-  <si>
-    <t>干涸的土地期盼着雨水</t>
-  </si>
-  <si>
-    <t>EI campo seco espera la lluvia</t>
+    <t>他干涸的土地期盼着雨水。</t>
+  </si>
+  <si>
+    <t>El campo seco espera la lluvia.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词mojado</t>
@@ -1602,13 +1491,10 @@
     <t>mojada（原形）</t>
   </si>
   <si>
-    <t>湿润的大地倒映着天空</t>
-  </si>
-  <si>
-    <t>la tierra mojada refleja el cielo</t>
-  </si>
-  <si>
-    <t>-o/a结尾形容词；反义词seco</t>
+    <t>他湿润的大地倒映着天空。</t>
+  </si>
+  <si>
+    <t>Él la tierra mojada refleja el cielo.</t>
   </si>
   <si>
     <t>Natural</t>
@@ -1617,13 +1503,13 @@
     <t>自然的</t>
   </si>
   <si>
-    <t>natural（原形）</t>
-  </si>
-  <si>
-    <t>蜂蜜的天然滋味</t>
-  </si>
-  <si>
-    <t>EI sabor natural de la miel</t>
+    <t>natural（原形） | 阴阳性同形: Natural</t>
+  </si>
+  <si>
+    <t>他蜂蜜的天然滋味。</t>
+  </si>
+  <si>
+    <t>El sabor natural de la miel.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词artificial</t>
@@ -1635,13 +1521,13 @@
     <t>人工的</t>
   </si>
   <si>
-    <t>artificiales（原形）</t>
-  </si>
-  <si>
-    <t>现代饮食中常见的人工甜味剂</t>
-  </si>
-  <si>
-    <t>los endulzantes artificiales comunes en la dieta moderna</t>
+    <t>artificiales（原形） | 阴阳性同形: Artificial</t>
+  </si>
+  <si>
+    <t>他现代饮食中常见的人工甜味剂。</t>
+  </si>
+  <si>
+    <t>Él los endulzantes artificiales comunes en la dieta moderna.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词natural</t>
@@ -1656,10 +1542,10 @@
     <t>moderna（原形）</t>
   </si>
   <si>
-    <t>与现代饮食中常见的人工甜味剂形成鲜明对比</t>
-  </si>
-  <si>
-    <t>contrasta con los endulzantes artificiales comunes en la dieta moderna</t>
+    <t>他与现代饮食中常见的人工甜味剂形成鲜明对比。</t>
+  </si>
+  <si>
+    <t>Él contrasta con los endulzantes artificiales comunes en la dieta moderna.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词antiguo</t>
@@ -1674,10 +1560,10 @@
     <t>antiguos（原形）</t>
   </si>
   <si>
-    <t>自远古时代就受人珍视</t>
-  </si>
-  <si>
-    <t>apreciado desde tiempos antiguos</t>
+    <t>他自远古时代就受人珍视。</t>
+  </si>
+  <si>
+    <t>Él apreciado desde tiempos antiguos.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词moderno</t>
@@ -1689,13 +1575,13 @@
     <t>正式的</t>
   </si>
   <si>
-    <t>formal（原形）</t>
-  </si>
-  <si>
-    <t>在市政厅举行的正式婚礼是一个公开活动</t>
-  </si>
-  <si>
-    <t>La boda formal en el ayuntamiento fue un acto publico</t>
+    <t>formal（原形） | 阴阳性同形: Formal</t>
+  </si>
+  <si>
+    <t>他在市政厅举行的正式婚礼是一个公开活动。</t>
+  </si>
+  <si>
+    <t>La boda formal en el ayuntamiento fue un acto publico.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词informal</t>
@@ -1707,13 +1593,13 @@
     <t>非正式的</t>
   </si>
   <si>
-    <t>informal（原形）</t>
-  </si>
-  <si>
-    <t>之后在花园里的非正式庆祝则只面向私密的宾客</t>
-  </si>
-  <si>
-    <t>La celebración informal en el jardin después fue solo para invitados privados</t>
+    <t>informal（原形） | 阴阳性同形: Informal</t>
+  </si>
+  <si>
+    <t>他之后在花园里的非正式庆祝则只面向私密的宾客。</t>
+  </si>
+  <si>
+    <t>La celebración informal en el jardin después fue solo para invitados privados.</t>
   </si>
   <si>
     <t>无阴阳性变化；反义词formal</t>
@@ -1728,12 +1614,6 @@
     <t>publico（原形）</t>
   </si>
   <si>
-    <t>在市政厅举行的正式婚礼是一个公开活动</t>
-  </si>
-  <si>
-    <t>La boda formal en el ayuntamiento fue un acto publico</t>
-  </si>
-  <si>
     <t>-o/a结尾形容词；反义词privado</t>
   </si>
   <si>
@@ -1746,10 +1626,7 @@
     <t>privados（原形）</t>
   </si>
   <si>
-    <t>之后在花园里的非正式庆祝则只面向私密的宾客</t>
-  </si>
-  <si>
-    <t>fue solo para invitados privados</t>
+    <t>Él fue solo para invitados privados.</t>
   </si>
   <si>
     <t>-o/a结尾形容词；反义词público</t>
@@ -1768,16 +1645,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -1831,19 +1708,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1880,7 +1757,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="lJIwTs">
+        <xdr:cNvPr id="2" name="Picture 2" descr="tDMpVY">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
@@ -2208,11 +2085,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CBC3F12-F870-49D2-A9FF-A18CDB09C163}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79ECBA5-1D5F-49B5-9488-972272CEF2F3}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -2223,1902 +2100,1922 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>366</v>
+        <v>343</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>367</v>
+        <v>344</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>369</v>
+        <v>334</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>393</v>
+        <v>356</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>394</v>
+        <v>357</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>396</v>
+        <v>369</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>399</v>
+        <v>362</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>400</v>
+        <v>363</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>403</v>
+        <v>374</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>404</v>
+        <v>375</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>405</v>
+        <v>376</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>406</v>
+        <v>377</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>407</v>
+        <v>378</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>409</v>
+        <v>380</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>411</v>
+        <v>382</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>412</v>
+        <v>383</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>413</v>
+        <v>384</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>414</v>
+        <v>385</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>415</v>
+        <v>386</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>416</v>
+        <v>387</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>417</v>
+        <v>388</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>418</v>
+        <v>389</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>419</v>
+        <v>390</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>420</v>
+        <v>391</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>421</v>
+        <v>392</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>422</v>
+        <v>393</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>423</v>
+        <v>382</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>424</v>
+        <v>383</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>425</v>
+        <v>394</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>426</v>
+        <v>395</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>427</v>
+        <v>396</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>429</v>
+        <v>398</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>430</v>
+        <v>399</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>432</v>
+        <v>401</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>433</v>
+        <v>402</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>434</v>
+        <v>403</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>436</v>
+        <v>405</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>437</v>
+        <v>406</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>439</v>
+        <v>408</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>440</v>
+        <v>409</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>441</v>
+        <v>410</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>445</v>
+        <v>414</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>446</v>
+        <v>415</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>448</v>
+        <v>417</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>449</v>
+        <v>418</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>450</v>
+        <v>419</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>451</v>
+        <v>420</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>452</v>
+        <v>421</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>453</v>
+        <v>422</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>454</v>
+        <v>423</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>456</v>
+        <v>425</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>457</v>
+        <v>426</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>458</v>
+        <v>427</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>461</v>
+        <v>430</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>462</v>
+        <v>431</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>463</v>
+        <v>432</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>464</v>
+        <v>433</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>465</v>
+        <v>422</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>466</v>
+        <v>423</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>467</v>
+        <v>434</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>468</v>
+        <v>435</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>469</v>
+        <v>436</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>470</v>
+        <v>437</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>471</v>
+        <v>438</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>473</v>
+        <v>440</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>481</v>
+        <v>448</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>482</v>
+        <v>449</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>485</v>
+        <v>452</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>486</v>
+        <v>453</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>487</v>
+        <v>454</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>488</v>
+        <v>455</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>491</v>
+        <v>458</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>492</v>
+        <v>459</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>493</v>
+        <v>460</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>494</v>
+        <v>461</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>495</v>
+        <v>462</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>497</v>
+        <v>464</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>498</v>
+        <v>41</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>499</v>
+        <v>465</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>500</v>
+        <v>466</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>501</v>
+        <v>467</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>502</v>
+        <v>468</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>503</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>504</v>
+        <v>469</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>505</v>
+        <v>470</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>506</v>
+        <v>471</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>507</v>
+        <v>467</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>508</v>
+        <v>468</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>509</v>
+        <v>52</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>510</v>
+        <v>472</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>511</v>
+        <v>473</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>512</v>
+        <v>474</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>513</v>
+        <v>475</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>514</v>
+        <v>476</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>515</v>
+        <v>270</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>516</v>
+        <v>259</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>517</v>
+        <v>477</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>518</v>
+        <v>261</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>519</v>
+        <v>478</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>520</v>
+        <v>479</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>521</v>
+        <v>480</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>522</v>
+        <v>65</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>523</v>
+        <v>481</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>524</v>
+        <v>67</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>525</v>
+        <v>482</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>526</v>
+        <v>483</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>527</v>
+        <v>484</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>528</v>
+        <v>485</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>529</v>
+        <v>486</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>532</v>
+        <v>489</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>533</v>
+        <v>76</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>534</v>
+        <v>490</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>535</v>
+        <v>491</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>536</v>
+        <v>492</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>537</v>
+        <v>493</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>538</v>
+        <v>494</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>539</v>
+        <v>495</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>540</v>
+        <v>496</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>541</v>
+        <v>497</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>542</v>
+        <v>498</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>543</v>
+        <v>499</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>544</v>
+        <v>500</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>545</v>
+        <v>501</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>546</v>
+        <v>502</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>547</v>
+        <v>503</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>548</v>
+        <v>504</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>549</v>
+        <v>505</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>550</v>
+        <v>506</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>551</v>
+        <v>507</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>552</v>
+        <v>508</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>553</v>
+        <v>509</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>554</v>
+        <v>510</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>555</v>
+        <v>511</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>556</v>
+        <v>512</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>557</v>
+        <v>513</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>558</v>
+        <v>514</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>559</v>
+        <v>515</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>560</v>
+        <v>516</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>561</v>
+        <v>517</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>562</v>
+        <v>518</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>563</v>
+        <v>519</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>564</v>
+        <v>520</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>565</v>
+        <v>521</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>566</v>
+        <v>522</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>567</v>
+        <v>523</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>568</v>
+        <v>524</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>569</v>
+        <v>525</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>570</v>
+        <v>526</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>571</v>
+        <v>527</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>572</v>
+        <v>528</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>573</v>
+        <v>517</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>574</v>
+        <v>518</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>575</v>
+        <v>529</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>530</v>
+      </c>
+      <c r="B96" t="s">
+        <v>531</v>
+      </c>
+      <c r="C96" t="s">
+        <v>532</v>
+      </c>
+      <c r="D96" t="s">
+        <v>523</v>
+      </c>
+      <c r="E96" t="s">
+        <v>533</v>
+      </c>
+      <c r="F96" t="s">
+        <v>534</v>
       </c>
     </row>
   </sheetData>
